--- a/currentbuild/StructureDefinition-lmdi-medication.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medication.xlsx
@@ -269,7 +269,7 @@
   </si>
   <si>
     <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}</t>
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}lmdi-medication-code-or-ingredient:Medication skal ha code.coding eller ingredient {code.coding.exists() or ingredient.exists()}</t>
   </si>
   <si>
     <t>NewRx/MedicationPrescribed@@ -465,7 +465,7 @@
 </t>
   </si>
   <si>
-    <t>Klassifisering av legemidlet, fortrinnsvis ved bruk av ATC-kode fra WHO ATC kodesystem. Ett legemiddel kan ha inntil én ATC-kode.</t>
+    <t>Klassifisering av legemidlet ved bruk av ATC-kode fra WHO ATC kodesystem. Ett legemiddel kan ha inntil én ATC-kode.</t>
   </si>
   <si>
     <t>Denne extension brukes for å angi legemidlets klassifisering i henhold til standardiserte kodesystemer, primært ATC-koder fra WHO.</t>
@@ -2848,7 +2848,7 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>77</v>

--- a/currentbuild/StructureDefinition-lmdi-medication.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medication.xlsx
@@ -931,10 +931,10 @@
     <t>Medication.code.coding:Varenummer.userSelected</t>
   </si>
   <si>
-    <t>Medication.code.coding:FestVirkestoff</t>
-  </si>
-  <si>
-    <t>FestVirkestoff</t>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff</t>
+  </si>
+  <si>
+    <t>FestLegemiddelVirkestoff</t>
   </si>
   <si>
     <t>FEST-id for legemiddel virkestoff</t>
@@ -943,28 +943,28 @@
     <t>Unik identifikator (LegemiddelVirkestoff_ID) for rekvirering på virkestoffnivå i FEST.</t>
   </si>
   <si>
-    <t>Medication.code.coding:FestVirkestoff.id</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:FestVirkestoff.extension</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:FestVirkestoff.system</t>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff.id</t>
+  </si>
+  <si>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff.extension</t>
+  </si>
+  <si>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff.system</t>
   </si>
   <si>
     <t>http://dmp.no/fhir/NamingSystem/festLegemiddelVirkestoff</t>
   </si>
   <si>
-    <t>Medication.code.coding:FestVirkestoff.version</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:FestVirkestoff.code</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:FestVirkestoff.display</t>
-  </si>
-  <si>
-    <t>Medication.code.coding:FestVirkestoff.userSelected</t>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff.version</t>
+  </si>
+  <si>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff.code</t>
+  </si>
+  <si>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff.display</t>
+  </si>
+  <si>
+    <t>Medication.code.coding:FestLegemiddelVirkestoff.userSelected</t>
   </si>
   <si>
     <t>Medication.code.coding:LokaltLegemiddel</t>
@@ -1284,7 +1284,7 @@
     <t>Virkestoff(er) som inngår i legemiddelet. Skal fylles ut hvis code ikke har verdi. Bør fylles ut hvis code.coding[LokaltLegemiddel] har verdi.</t>
   </si>
   <si>
-    <t>For legemidler identifisert med FEST-koder (FestLegemiddeldose, FestLegemiddelMerkevare, FestLegemiddelpakning, FestVirkestoff, Varenummer) eller SNOMED CT er ingredient valgfritt, da virkestoffinformasjon kan hentes fra disse katalogene. For lokale legemidler anbefales det å oppgi ingredient for bedre sporbarhet.</t>
+    <t>For legemidler identifisert med FEST-koder (FestLegemiddeldose, FestLegemiddelMerkevare, FestLegemiddelpakning, FestLegemiddelVirkestoff, Varenummer) eller SNOMED CT er ingredient valgfritt, da virkestoffinformasjon kan hentes fra disse katalogene. For lokale legemidler anbefales det å oppgi ingredient for bedre sporbarhet.</t>
   </si>
   <si>
     <t>.scopesRole[typeCode=INGR]</t>

--- a/currentbuild/StructureDefinition-lmdi-medication.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4637" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4637" uniqueCount="459">
   <si>
     <t>Property</t>
   </si>
@@ -854,6 +854,9 @@
   </si>
   <si>
     <t>Medication.code.coding:FestLegemiddelMerkevare.display</t>
+  </si>
+  <si>
+    <t>Varenavn fra FEST</t>
   </si>
   <si>
     <t>Medication.code.coding:FestLegemiddelMerkevare.userSelected</t>
@@ -6183,7 +6186,7 @@
         <v>171</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="M39" t="s" s="2">
         <v>229</v>
@@ -6268,7 +6271,7 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="B40" t="s" s="2">
         <v>235</v>
@@ -6384,13 +6387,13 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B41" t="s" s="2">
         <v>182</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>77</v>
@@ -6415,10 +6418,10 @@
         <v>183</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="N41" t="s" s="2">
         <v>186</v>
@@ -6502,7 +6505,7 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B42" t="s" s="2">
         <v>197</v>
@@ -6614,7 +6617,7 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B43" t="s" s="2">
         <v>199</v>
@@ -6728,7 +6731,7 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B44" t="s" s="2">
         <v>201</v>
@@ -6776,7 +6779,7 @@
         <v>77</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>77</v>
@@ -6844,7 +6847,7 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B45" t="s" s="2">
         <v>211</v>
@@ -6958,7 +6961,7 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B46" t="s" s="2">
         <v>219</v>
@@ -7072,7 +7075,7 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>227</v>
@@ -7186,7 +7189,7 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>235</v>
@@ -7302,13 +7305,13 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>182</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -7333,10 +7336,10 @@
         <v>183</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="N49" t="s" s="2">
         <v>186</v>
@@ -7420,7 +7423,7 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>197</v>
@@ -7532,7 +7535,7 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>199</v>
@@ -7646,7 +7649,7 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>201</v>
@@ -7694,7 +7697,7 @@
         <v>77</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>77</v>
@@ -7762,7 +7765,7 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>211</v>
@@ -7876,7 +7879,7 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>219</v>
@@ -7905,7 +7908,7 @@
         <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="M54" t="s" s="2">
         <v>221</v>
@@ -7990,7 +7993,7 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>227</v>
@@ -8104,7 +8107,7 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B56" t="s" s="2">
         <v>235</v>
@@ -8220,13 +8223,13 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B57" t="s" s="2">
         <v>182</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>77</v>
@@ -8251,10 +8254,10 @@
         <v>183</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="N57" t="s" s="2">
         <v>186</v>
@@ -8338,7 +8341,7 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B58" t="s" s="2">
         <v>197</v>
@@ -8450,7 +8453,7 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B59" t="s" s="2">
         <v>199</v>
@@ -8564,7 +8567,7 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B60" t="s" s="2">
         <v>201</v>
@@ -8612,7 +8615,7 @@
         <v>77</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>77</v>
@@ -8680,7 +8683,7 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B61" t="s" s="2">
         <v>211</v>
@@ -8794,7 +8797,7 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B62" t="s" s="2">
         <v>219</v>
@@ -8908,7 +8911,7 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B63" t="s" s="2">
         <v>227</v>
@@ -9022,7 +9025,7 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B64" t="s" s="2">
         <v>235</v>
@@ -9138,13 +9141,13 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B65" t="s" s="2">
         <v>182</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>77</v>
@@ -9169,10 +9172,10 @@
         <v>183</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="N65" t="s" s="2">
         <v>186</v>
@@ -9256,7 +9259,7 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B66" t="s" s="2">
         <v>197</v>
@@ -9368,7 +9371,7 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B67" t="s" s="2">
         <v>199</v>
@@ -9482,7 +9485,7 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B68" t="s" s="2">
         <v>201</v>
@@ -9530,7 +9533,7 @@
         <v>77</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>77</v>
@@ -9598,7 +9601,7 @@
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B69" t="s" s="2">
         <v>211</v>
@@ -9712,7 +9715,7 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B70" t="s" s="2">
         <v>219</v>
@@ -9741,7 +9744,7 @@
         <v>107</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="M70" t="s" s="2">
         <v>221</v>
@@ -9826,7 +9829,7 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B71" t="s" s="2">
         <v>227</v>
@@ -9855,7 +9858,7 @@
         <v>171</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="M71" t="s" s="2">
         <v>229</v>
@@ -9940,7 +9943,7 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B72" t="s" s="2">
         <v>235</v>
@@ -10056,13 +10059,13 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B73" t="s" s="2">
         <v>182</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>77</v>
@@ -10087,10 +10090,10 @@
         <v>183</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="N73" t="s" s="2">
         <v>186</v>
@@ -10174,7 +10177,7 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B74" t="s" s="2">
         <v>197</v>
@@ -10286,7 +10289,7 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B75" t="s" s="2">
         <v>199</v>
@@ -10400,7 +10403,7 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B76" t="s" s="2">
         <v>201</v>
@@ -10448,7 +10451,7 @@
         <v>77</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>77</v>
@@ -10516,7 +10519,7 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B77" t="s" s="2">
         <v>211</v>
@@ -10630,7 +10633,7 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B78" t="s" s="2">
         <v>219</v>
@@ -10659,7 +10662,7 @@
         <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="M78" t="s" s="2">
         <v>221</v>
@@ -10744,7 +10747,7 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B79" t="s" s="2">
         <v>227</v>
@@ -10858,7 +10861,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>235</v>
@@ -10974,10 +10977,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11003,16 +11006,16 @@
         <v>171</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11061,7 +11064,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11079,21 +11082,21 @@
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11119,13 +11122,13 @@
         <v>107</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11151,13 +11154,13 @@
         <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -11175,7 +11178,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11193,7 +11196,7 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -11204,10 +11207,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11230,13 +11233,13 @@
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11287,7 +11290,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11302,24 +11305,24 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11345,13 +11348,13 @@
         <v>160</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11377,13 +11380,13 @@
         <v>77</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>77</v>
@@ -11401,7 +11404,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11416,24 +11419,24 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11542,10 +11545,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11656,10 +11659,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11685,13 +11688,13 @@
         <v>183</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="M87" t="s" s="2">
         <v>185</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="O87" t="s" s="2">
         <v>187</v>
@@ -11770,10 +11773,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11882,10 +11885,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11996,10 +11999,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12112,10 +12115,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12226,10 +12229,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12255,7 +12258,7 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M92" t="s" s="2">
         <v>221</v>
@@ -12340,10 +12343,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12454,10 +12457,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12570,13 +12573,13 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>77</v>
@@ -12601,7 +12604,7 @@
         <v>183</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="M95" t="s" s="2">
         <v>185</v>
@@ -12688,10 +12691,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12800,10 +12803,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12914,10 +12917,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12962,7 +12965,7 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>77</v>
@@ -13030,10 +13033,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13144,10 +13147,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13173,7 +13176,7 @@
         <v>107</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M100" t="s" s="2">
         <v>221</v>
@@ -13258,10 +13261,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13287,7 +13290,7 @@
         <v>171</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M101" t="s" s="2">
         <v>229</v>
@@ -13372,10 +13375,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13488,13 +13491,13 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>77</v>
@@ -13519,7 +13522,7 @@
         <v>183</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="M103" t="s" s="2">
         <v>185</v>
@@ -13606,10 +13609,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13718,10 +13721,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13832,10 +13835,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13880,7 +13883,7 @@
         <v>77</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>77</v>
@@ -13948,10 +13951,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14062,10 +14065,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14091,7 +14094,7 @@
         <v>107</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>221</v>
@@ -14176,10 +14179,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14290,10 +14293,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14406,10 +14409,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14435,16 +14438,16 @@
         <v>171</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>77</v>
@@ -14493,7 +14496,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14511,21 +14514,21 @@
         <v>77</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14548,13 +14551,13 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14605,7 +14608,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14623,7 +14626,7 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
@@ -14634,10 +14637,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14660,16 +14663,16 @@
         <v>77</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -14719,7 +14722,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14737,7 +14740,7 @@
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>
@@ -14748,10 +14751,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14860,10 +14863,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14974,14 +14977,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15003,10 +15006,10 @@
         <v>132</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>149</v>
@@ -15061,7 +15064,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15090,10 +15093,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15116,17 +15119,17 @@
         <v>77</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>77</v>
@@ -15163,7 +15166,7 @@
         <v>77</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="AC117" s="2"/>
       <c r="AD117" t="s" s="2">
@@ -15173,7 +15176,7 @@
         <v>136</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>87</v>
@@ -15191,24 +15194,24 @@
         <v>166</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>77</v>
@@ -15230,17 +15233,17 @@
         <v>77</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>77</v>
@@ -15289,7 +15292,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>87</v>
@@ -15307,24 +15310,24 @@
         <v>166</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>77</v>
@@ -15349,14 +15352,14 @@
         <v>160</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>77</v>
@@ -15403,7 +15406,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>87</v>
@@ -15421,21 +15424,21 @@
         <v>166</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15461,14 +15464,14 @@
         <v>236</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>77</v>
@@ -15517,7 +15520,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15535,7 +15538,7 @@
         <v>77</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>77</v>
@@ -15546,10 +15549,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15572,13 +15575,13 @@
         <v>77</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15629,7 +15632,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -15644,24 +15647,24 @@
         <v>99</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15684,13 +15687,13 @@
         <v>77</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -15741,7 +15744,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -15756,10 +15759,10 @@
         <v>99</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -15770,10 +15773,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15882,10 +15885,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15996,14 +15999,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -16025,10 +16028,10 @@
         <v>132</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>149</v>
@@ -16083,7 +16086,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16112,10 +16115,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16141,10 +16144,10 @@
         <v>171</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16195,7 +16198,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16210,7 +16213,7 @@
         <v>99</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>157</v>
@@ -16219,15 +16222,15 @@
         <v>77</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16250,13 +16253,13 @@
         <v>77</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -16307,7 +16310,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -16322,16 +16325,16 @@
         <v>99</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
     </row>
   </sheetData>

--- a/currentbuild/StructureDefinition-lmdi-medication.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medication.xlsx
@@ -991,7 +991,7 @@
     <t>Medication.code.coding:LokaltLegemiddel.system</t>
   </si>
   <si>
-    <t>http://fh.no/fhir/NamingSystem/lokaltVirkemiddel</t>
+    <t>http://fh.no/fhir/NamingSystem/lokaltLegemiddel</t>
   </si>
   <si>
     <t>Medication.code.coding:LokaltLegemiddel.version</t>

--- a/currentbuild/StructureDefinition-lmdi-medication.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medication.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.0.8</t>
+    <t>1.1.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -991,7 +991,7 @@
     <t>Medication.code.coding:LokaltLegemiddel.system</t>
   </si>
   <si>
-    <t>http://fh.no/fhir/NamingSystem/lokaltLegemiddel</t>
+    <t>http://fhi.no/fhir/NamingSystem/lokaltLegemiddel</t>
   </si>
   <si>
     <t>Medication.code.coding:LokaltLegemiddel.version</t>

--- a/currentbuild/StructureDefinition-lmdi-medication.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4637" uniqueCount="459">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4637" uniqueCount="460">
   <si>
     <t>Property</t>
   </si>
@@ -735,7 +735,7 @@
     <t>Medication.code.coding.display</t>
   </si>
   <si>
-    <t>Representation defined by the system</t>
+    <t>NavnFormStyrke fra FEST</t>
   </si>
   <si>
     <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
@@ -856,7 +856,7 @@
     <t>Medication.code.coding:FestLegemiddelMerkevare.display</t>
   </si>
   <si>
-    <t>Varenavn fra FEST</t>
+    <t>Varenavn eller NavnFormStyrke fra FEST</t>
   </si>
   <si>
     <t>Medication.code.coding:FestLegemiddelMerkevare.userSelected</t>
@@ -1046,6 +1046,9 @@
   </si>
   <si>
     <t>Medication.code.coding:SCT.display</t>
+  </si>
+  <si>
+    <t>Representation defined by the system</t>
   </si>
   <si>
     <t>Medication.code.coding:SCT.userSelected</t>
@@ -7104,7 +7107,7 @@
         <v>171</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="M47" t="s" s="2">
         <v>229</v>
@@ -8022,7 +8025,7 @@
         <v>171</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>228</v>
+        <v>268</v>
       </c>
       <c r="M55" t="s" s="2">
         <v>229</v>
@@ -10776,7 +10779,7 @@
         <v>171</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>228</v>
+        <v>332</v>
       </c>
       <c r="M79" t="s" s="2">
         <v>229</v>
@@ -10861,7 +10864,7 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B80" t="s" s="2">
         <v>235</v>
@@ -10977,10 +10980,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11006,16 +11009,16 @@
         <v>171</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11064,7 +11067,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11082,21 +11085,21 @@
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11122,13 +11125,13 @@
         <v>107</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11154,13 +11157,13 @@
         <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -11178,7 +11181,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11196,7 +11199,7 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -11207,10 +11210,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11233,13 +11236,13 @@
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11290,7 +11293,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11305,24 +11308,24 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11348,13 +11351,13 @@
         <v>160</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11380,13 +11383,13 @@
         <v>77</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>77</v>
@@ -11404,7 +11407,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11419,24 +11422,24 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11545,10 +11548,10 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -11659,10 +11662,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11688,13 +11691,13 @@
         <v>183</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="M87" t="s" s="2">
         <v>185</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O87" t="s" s="2">
         <v>187</v>
@@ -11773,10 +11776,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11885,10 +11888,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -11999,10 +12002,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12115,10 +12118,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12229,10 +12232,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12258,7 +12261,7 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M92" t="s" s="2">
         <v>221</v>
@@ -12343,10 +12346,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12372,7 +12375,7 @@
         <v>171</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>228</v>
+        <v>332</v>
       </c>
       <c r="M93" t="s" s="2">
         <v>229</v>
@@ -12457,10 +12460,10 @@
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12573,13 +12576,13 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>77</v>
@@ -12604,7 +12607,7 @@
         <v>183</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="M95" t="s" s="2">
         <v>185</v>
@@ -12691,10 +12694,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12803,10 +12806,10 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -12917,10 +12920,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12965,7 +12968,7 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>77</v>
@@ -13033,10 +13036,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13147,10 +13150,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13176,7 +13179,7 @@
         <v>107</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="M100" t="s" s="2">
         <v>221</v>
@@ -13261,10 +13264,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13290,7 +13293,7 @@
         <v>171</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="M101" t="s" s="2">
         <v>229</v>
@@ -13375,10 +13378,10 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13491,10 +13494,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C103" t="s" s="2">
         <v>321</v>
@@ -13522,7 +13525,7 @@
         <v>183</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="M103" t="s" s="2">
         <v>185</v>
@@ -13609,10 +13612,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13721,10 +13724,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -13835,10 +13838,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13951,10 +13954,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14065,10 +14068,10 @@
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14094,7 +14097,7 @@
         <v>107</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="M108" t="s" s="2">
         <v>221</v>
@@ -14179,10 +14182,10 @@
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14208,7 +14211,7 @@
         <v>171</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>228</v>
+        <v>332</v>
       </c>
       <c r="M109" t="s" s="2">
         <v>229</v>
@@ -14293,10 +14296,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14409,10 +14412,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14438,16 +14441,16 @@
         <v>171</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>77</v>
@@ -14496,7 +14499,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14514,21 +14517,21 @@
         <v>77</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14551,13 +14554,13 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14608,7 +14611,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14626,7 +14629,7 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
@@ -14637,10 +14640,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14663,16 +14666,16 @@
         <v>77</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -14722,7 +14725,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14740,7 +14743,7 @@
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>
@@ -14751,10 +14754,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14863,10 +14866,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -14977,14 +14980,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15006,10 +15009,10 @@
         <v>132</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N116" t="s" s="2">
         <v>149</v>
@@ -15064,7 +15067,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15093,10 +15096,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15119,17 +15122,17 @@
         <v>77</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>77</v>
@@ -15166,7 +15169,7 @@
         <v>77</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AC117" s="2"/>
       <c r="AD117" t="s" s="2">
@@ -15176,7 +15179,7 @@
         <v>136</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>87</v>
@@ -15194,24 +15197,24 @@
         <v>166</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>77</v>
@@ -15233,17 +15236,17 @@
         <v>77</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>77</v>
@@ -15292,7 +15295,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>87</v>
@@ -15310,24 +15313,24 @@
         <v>166</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>77</v>
@@ -15352,14 +15355,14 @@
         <v>160</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>77</v>
@@ -15406,7 +15409,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>87</v>
@@ -15424,21 +15427,21 @@
         <v>166</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15464,14 +15467,14 @@
         <v>236</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>77</v>
@@ -15520,7 +15523,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15538,7 +15541,7 @@
         <v>77</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>77</v>
@@ -15549,10 +15552,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15575,13 +15578,13 @@
         <v>77</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15632,7 +15635,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -15647,24 +15650,24 @@
         <v>99</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15687,13 +15690,13 @@
         <v>77</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -15744,7 +15747,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -15759,10 +15762,10 @@
         <v>99</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -15773,10 +15776,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15885,10 +15888,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -15999,14 +16002,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -16028,10 +16031,10 @@
         <v>132</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>149</v>
@@ -16086,7 +16089,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16115,10 +16118,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16144,10 +16147,10 @@
         <v>171</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16198,7 +16201,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16213,7 +16216,7 @@
         <v>99</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL126" t="s" s="2">
         <v>157</v>
@@ -16222,15 +16225,15 @@
         <v>77</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16253,13 +16256,13 @@
         <v>77</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -16310,7 +16313,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -16325,16 +16328,16 @@
         <v>99</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
     </row>
   </sheetData>

--- a/currentbuild/StructureDefinition-lmdi-medication.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medication.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4637" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4637" uniqueCount="461">
   <si>
     <t>Property</t>
   </si>
@@ -465,7 +465,10 @@
 </t>
   </si>
   <si>
-    <t>Klassifisering av legemidlet ved bruk av ATC-kode fra WHO ATC kodesystem. Ett legemiddel kan ha inntil én ATC-kode.</t>
+    <t>Klassifisering av legemidlet ved bruk av ATC-kode fra WHO ATC kodesystem.</t>
+  </si>
+  <si>
+    <t>Klassifisering av legemidlet ved bruk av ATC-kode fra WHO ATC kodesystem. Et legemiddel har i utgangspunktet kun én ATC-kode.</t>
   </si>
   <si>
     <t>Denne extension brukes for å angi legemidlets klassifisering i henhold til standardiserte kodesystemer, primært ATC-koder fra WHO.</t>
@@ -2854,7 +2857,7 @@
         <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H10" t="s" s="2">
         <v>77</v>
@@ -2872,10 +2875,10 @@
         <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O10" s="2"/>
       <c r="P10" t="s" s="2">
@@ -2934,7 +2937,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>138</v>
@@ -2954,14 +2957,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2983,16 +2986,16 @@
         <v>132</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -3041,7 +3044,7 @@
         <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -3070,10 +3073,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -3096,16 +3099,16 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -3155,7 +3158,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -3173,10 +3176,10 @@
         <v>77</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AN12" t="s" s="2">
         <v>77</v>
@@ -3184,10 +3187,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -3210,16 +3213,16 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="N13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
@@ -3245,11 +3248,11 @@
         <v>77</v>
       </c>
       <c r="X13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="Y13" s="2"/>
       <c r="Z13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA13" t="s" s="2">
         <v>77</v>
@@ -3267,7 +3270,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -3282,24 +3285,24 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -3322,13 +3325,13 @@
         <v>77</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -3379,7 +3382,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3397,7 +3400,7 @@
         <v>77</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM14" t="s" s="2">
         <v>77</v>
@@ -3408,14 +3411,14 @@
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3437,13 +3440,13 @@
         <v>132</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3484,16 +3487,16 @@
         <v>135</v>
       </c>
       <c r="AC15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3511,7 +3514,7 @@
         <v>77</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>77</v>
@@ -3522,10 +3525,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3548,19 +3551,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3597,17 +3600,17 @@
         <v>77</v>
       </c>
       <c r="AB16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AC16" s="2"/>
       <c r="AD16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE16" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3625,24 +3628,24 @@
         <v>77</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D17" t="s" s="2">
         <v>77</v>
@@ -3664,19 +3667,19 @@
         <v>88</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3725,7 +3728,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3743,21 +3746,21 @@
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3780,13 +3783,13 @@
         <v>77</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3837,7 +3840,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3855,7 +3858,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3866,14 +3869,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3895,13 +3898,13 @@
         <v>132</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3942,16 +3945,16 @@
         <v>135</v>
       </c>
       <c r="AC19" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE19" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3969,7 +3972,7 @@
         <v>77</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3980,10 +3983,10 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4009,16 +4012,16 @@
         <v>101</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
@@ -4028,7 +4031,7 @@
         <v>77</v>
       </c>
       <c r="S20" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="T20" t="s" s="2">
         <v>77</v>
@@ -4067,7 +4070,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -4085,21 +4088,21 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -4122,16 +4125,16 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
@@ -4181,7 +4184,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -4199,21 +4202,21 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4239,14 +4242,14 @@
         <v>107</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -4295,7 +4298,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -4313,21 +4316,21 @@
         <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN22" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4350,17 +4353,17 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4409,7 +4412,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4427,21 +4430,21 @@
         <v>77</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN23" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4464,19 +4467,19 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
@@ -4525,7 +4528,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4543,24 +4546,24 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>77</v>
@@ -4582,19 +4585,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4643,7 +4646,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4661,21 +4664,21 @@
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4698,13 +4701,13 @@
         <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4755,7 +4758,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4773,7 +4776,7 @@
         <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4784,14 +4787,14 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
@@ -4813,13 +4816,13 @@
         <v>132</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -4860,16 +4863,16 @@
         <v>135</v>
       </c>
       <c r="AC27" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD27" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE27" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4887,7 +4890,7 @@
         <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4898,10 +4901,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4927,16 +4930,16 @@
         <v>101</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>77</v>
@@ -4946,7 +4949,7 @@
         <v>77</v>
       </c>
       <c r="S28" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="T28" t="s" s="2">
         <v>77</v>
@@ -4985,7 +4988,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5003,21 +5006,21 @@
         <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5040,16 +5043,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -5099,7 +5102,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5117,21 +5120,21 @@
         <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5157,14 +5160,14 @@
         <v>107</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
@@ -5213,7 +5216,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5231,21 +5234,21 @@
         <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5268,17 +5271,17 @@
         <v>88</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N31" s="2"/>
       <c r="O31" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5327,7 +5330,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5345,21 +5348,21 @@
         <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM31" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5382,19 +5385,19 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>77</v>
@@ -5443,7 +5446,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5461,24 +5464,24 @@
         <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C33" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="D33" t="s" s="2">
         <v>77</v>
@@ -5500,19 +5503,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5561,7 +5564,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5579,21 +5582,21 @@
         <v>77</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM33" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5616,13 +5619,13 @@
         <v>77</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N34" s="2"/>
       <c r="O34" s="2"/>
@@ -5673,7 +5676,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5691,7 +5694,7 @@
         <v>77</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM34" t="s" s="2">
         <v>77</v>
@@ -5702,14 +5705,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -5731,13 +5734,13 @@
         <v>132</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5778,16 +5781,16 @@
         <v>135</v>
       </c>
       <c r="AC35" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD35" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE35" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5805,7 +5808,7 @@
         <v>77</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5816,10 +5819,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5845,16 +5848,16 @@
         <v>101</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5864,7 +5867,7 @@
         <v>77</v>
       </c>
       <c r="S36" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="T36" t="s" s="2">
         <v>77</v>
@@ -5903,7 +5906,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5921,21 +5924,21 @@
         <v>77</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM36" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5958,16 +5961,16 @@
         <v>88</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6017,7 +6020,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6035,21 +6038,21 @@
         <v>77</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM37" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6075,14 +6078,14 @@
         <v>107</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6131,7 +6134,7 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6149,21 +6152,21 @@
         <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM38" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6186,17 +6189,17 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>77</v>
@@ -6245,7 +6248,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -6263,21 +6266,21 @@
         <v>77</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM39" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6300,19 +6303,19 @@
         <v>88</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>77</v>
@@ -6361,7 +6364,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -6379,24 +6382,24 @@
         <v>77</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM40" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C41" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="D41" t="s" s="2">
         <v>77</v>
@@ -6418,19 +6421,19 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>77</v>
@@ -6479,7 +6482,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6497,21 +6500,21 @@
         <v>77</v>
       </c>
       <c r="AL41" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM41" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6534,13 +6537,13 @@
         <v>77</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6591,7 +6594,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6609,7 +6612,7 @@
         <v>77</v>
       </c>
       <c r="AL42" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM42" t="s" s="2">
         <v>77</v>
@@ -6620,14 +6623,14 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -6649,13 +6652,13 @@
         <v>132</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6696,16 +6699,16 @@
         <v>135</v>
       </c>
       <c r="AC43" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD43" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE43" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6723,7 +6726,7 @@
         <v>77</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM43" t="s" s="2">
         <v>77</v>
@@ -6734,10 +6737,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6763,16 +6766,16 @@
         <v>101</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6782,7 +6785,7 @@
         <v>77</v>
       </c>
       <c r="S44" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="T44" t="s" s="2">
         <v>77</v>
@@ -6821,7 +6824,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6839,21 +6842,21 @@
         <v>77</v>
       </c>
       <c r="AL44" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM44" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN44" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6876,16 +6879,16 @@
         <v>88</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O45" s="2"/>
       <c r="P45" t="s" s="2">
@@ -6935,7 +6938,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6953,21 +6956,21 @@
         <v>77</v>
       </c>
       <c r="AL45" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM45" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6993,14 +6996,14 @@
         <v>107</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>77</v>
@@ -7049,7 +7052,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -7067,21 +7070,21 @@
         <v>77</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7104,17 +7107,17 @@
         <v>88</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N47" s="2"/>
       <c r="O47" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>77</v>
@@ -7163,7 +7166,7 @@
         <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -7181,21 +7184,21 @@
         <v>77</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7218,19 +7221,19 @@
         <v>88</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -7279,7 +7282,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7297,24 +7300,24 @@
         <v>77</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>77</v>
@@ -7336,19 +7339,19 @@
         <v>88</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>77</v>
@@ -7397,7 +7400,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7415,21 +7418,21 @@
         <v>77</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7452,13 +7455,13 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7509,7 +7512,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7527,7 +7530,7 @@
         <v>77</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>77</v>
@@ -7538,14 +7541,14 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E51" s="2"/>
       <c r="F51" t="s" s="2">
@@ -7567,13 +7570,13 @@
         <v>132</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -7614,16 +7617,16 @@
         <v>135</v>
       </c>
       <c r="AC51" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD51" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE51" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -7641,7 +7644,7 @@
         <v>77</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>77</v>
@@ -7652,10 +7655,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -7681,16 +7684,16 @@
         <v>101</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>77</v>
@@ -7700,7 +7703,7 @@
         <v>77</v>
       </c>
       <c r="S52" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="T52" t="s" s="2">
         <v>77</v>
@@ -7739,7 +7742,7 @@
         <v>77</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -7757,21 +7760,21 @@
         <v>77</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -7794,16 +7797,16 @@
         <v>88</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O53" s="2"/>
       <c r="P53" t="s" s="2">
@@ -7853,7 +7856,7 @@
         <v>77</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -7871,21 +7874,21 @@
         <v>77</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -7911,14 +7914,14 @@
         <v>107</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>77</v>
@@ -7967,7 +7970,7 @@
         <v>77</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>78</v>
@@ -7985,21 +7988,21 @@
         <v>77</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8022,17 +8025,17 @@
         <v>88</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>77</v>
@@ -8081,7 +8084,7 @@
         <v>77</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8099,21 +8102,21 @@
         <v>77</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8136,19 +8139,19 @@
         <v>88</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>77</v>
@@ -8197,7 +8200,7 @@
         <v>77</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8215,24 +8218,24 @@
         <v>77</v>
       </c>
       <c r="AL56" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM56" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN56" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="D57" t="s" s="2">
         <v>77</v>
@@ -8254,19 +8257,19 @@
         <v>88</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O57" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>77</v>
@@ -8315,7 +8318,7 @@
         <v>77</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>78</v>
@@ -8333,21 +8336,21 @@
         <v>77</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8370,13 +8373,13 @@
         <v>77</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -8427,7 +8430,7 @@
         <v>77</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>78</v>
@@ -8445,7 +8448,7 @@
         <v>77</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>77</v>
@@ -8456,14 +8459,14 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E59" s="2"/>
       <c r="F59" t="s" s="2">
@@ -8485,13 +8488,13 @@
         <v>132</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -8532,16 +8535,16 @@
         <v>135</v>
       </c>
       <c r="AC59" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD59" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE59" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>78</v>
@@ -8559,7 +8562,7 @@
         <v>77</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>77</v>
@@ -8570,10 +8573,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8599,16 +8602,16 @@
         <v>101</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>77</v>
@@ -8618,7 +8621,7 @@
         <v>77</v>
       </c>
       <c r="S60" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="T60" t="s" s="2">
         <v>77</v>
@@ -8657,7 +8660,7 @@
         <v>77</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>78</v>
@@ -8675,21 +8678,21 @@
         <v>77</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8712,16 +8715,16 @@
         <v>88</v>
       </c>
       <c r="K61" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -8771,7 +8774,7 @@
         <v>77</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>78</v>
@@ -8789,21 +8792,21 @@
         <v>77</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8829,14 +8832,14 @@
         <v>107</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>77</v>
@@ -8885,7 +8888,7 @@
         <v>77</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>78</v>
@@ -8903,21 +8906,21 @@
         <v>77</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -8940,17 +8943,17 @@
         <v>88</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>77</v>
@@ -8999,7 +9002,7 @@
         <v>77</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9017,21 +9020,21 @@
         <v>77</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN63" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9054,19 +9057,19 @@
         <v>88</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>77</v>
@@ -9115,7 +9118,7 @@
         <v>77</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>78</v>
@@ -9133,24 +9136,24 @@
         <v>77</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN64" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="D65" t="s" s="2">
         <v>77</v>
@@ -9172,19 +9175,19 @@
         <v>88</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>77</v>
@@ -9233,7 +9236,7 @@
         <v>77</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>78</v>
@@ -9251,21 +9254,21 @@
         <v>77</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9288,13 +9291,13 @@
         <v>77</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N66" s="2"/>
       <c r="O66" s="2"/>
@@ -9345,7 +9348,7 @@
         <v>77</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9363,7 +9366,7 @@
         <v>77</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>77</v>
@@ -9374,14 +9377,14 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E67" s="2"/>
       <c r="F67" t="s" s="2">
@@ -9403,13 +9406,13 @@
         <v>132</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9450,16 +9453,16 @@
         <v>135</v>
       </c>
       <c r="AC67" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD67" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE67" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9477,7 +9480,7 @@
         <v>77</v>
       </c>
       <c r="AL67" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM67" t="s" s="2">
         <v>77</v>
@@ -9488,10 +9491,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9517,16 +9520,16 @@
         <v>101</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>77</v>
@@ -9536,7 +9539,7 @@
         <v>77</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>77</v>
@@ -9575,7 +9578,7 @@
         <v>77</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -9593,21 +9596,21 @@
         <v>77</v>
       </c>
       <c r="AL68" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM68" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN68" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9630,16 +9633,16 @@
         <v>88</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N69" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O69" s="2"/>
       <c r="P69" t="s" s="2">
@@ -9689,7 +9692,7 @@
         <v>77</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -9707,21 +9710,21 @@
         <v>77</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN69" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9747,14 +9750,14 @@
         <v>107</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>77</v>
@@ -9803,7 +9806,7 @@
         <v>77</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -9821,21 +9824,21 @@
         <v>77</v>
       </c>
       <c r="AL70" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM70" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9858,17 +9861,17 @@
         <v>88</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>77</v>
@@ -9917,7 +9920,7 @@
         <v>77</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -9935,21 +9938,21 @@
         <v>77</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -9972,19 +9975,19 @@
         <v>88</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>77</v>
@@ -10033,7 +10036,7 @@
         <v>77</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>78</v>
@@ -10051,24 +10054,24 @@
         <v>77</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D73" t="s" s="2">
         <v>77</v>
@@ -10090,19 +10093,19 @@
         <v>88</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>77</v>
@@ -10151,7 +10154,7 @@
         <v>77</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10169,21 +10172,21 @@
         <v>77</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10206,13 +10209,13 @@
         <v>77</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" s="2"/>
@@ -10263,7 +10266,7 @@
         <v>77</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10281,7 +10284,7 @@
         <v>77</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>77</v>
@@ -10292,14 +10295,14 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E75" s="2"/>
       <c r="F75" t="s" s="2">
@@ -10321,13 +10324,13 @@
         <v>132</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -10368,16 +10371,16 @@
         <v>135</v>
       </c>
       <c r="AC75" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD75" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE75" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10395,7 +10398,7 @@
         <v>77</v>
       </c>
       <c r="AL75" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM75" t="s" s="2">
         <v>77</v>
@@ -10406,10 +10409,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -10435,16 +10438,16 @@
         <v>101</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>77</v>
@@ -10454,7 +10457,7 @@
         <v>77</v>
       </c>
       <c r="S76" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="T76" t="s" s="2">
         <v>77</v>
@@ -10493,7 +10496,7 @@
         <v>77</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -10511,21 +10514,21 @@
         <v>77</v>
       </c>
       <c r="AL76" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM76" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN76" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -10548,16 +10551,16 @@
         <v>88</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O77" s="2"/>
       <c r="P77" t="s" s="2">
@@ -10607,7 +10610,7 @@
         <v>77</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>78</v>
@@ -10625,21 +10628,21 @@
         <v>77</v>
       </c>
       <c r="AL77" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM77" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN77" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -10665,14 +10668,14 @@
         <v>107</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>77</v>
@@ -10721,7 +10724,7 @@
         <v>77</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>78</v>
@@ -10739,21 +10742,21 @@
         <v>77</v>
       </c>
       <c r="AL78" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM78" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN78" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -10776,17 +10779,17 @@
         <v>88</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P79" t="s" s="2">
         <v>77</v>
@@ -10835,7 +10838,7 @@
         <v>77</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>78</v>
@@ -10853,21 +10856,21 @@
         <v>77</v>
       </c>
       <c r="AL79" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM79" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN79" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -10890,19 +10893,19 @@
         <v>88</v>
       </c>
       <c r="K80" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>77</v>
@@ -10951,7 +10954,7 @@
         <v>77</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -10969,21 +10972,21 @@
         <v>77</v>
       </c>
       <c r="AL80" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM80" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN80" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11006,19 +11009,19 @@
         <v>88</v>
       </c>
       <c r="K81" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>77</v>
@@ -11067,7 +11070,7 @@
         <v>77</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11085,21 +11088,21 @@
         <v>77</v>
       </c>
       <c r="AL81" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AM81" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN81" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11125,13 +11128,13 @@
         <v>107</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -11157,13 +11160,13 @@
         <v>77</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="Y82" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="Z82" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>77</v>
@@ -11181,7 +11184,7 @@
         <v>77</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11199,7 +11202,7 @@
         <v>77</v>
       </c>
       <c r="AL82" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="AM82" t="s" s="2">
         <v>77</v>
@@ -11210,10 +11213,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11236,13 +11239,13 @@
         <v>88</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -11293,7 +11296,7 @@
         <v>77</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11308,24 +11311,24 @@
         <v>99</v>
       </c>
       <c r="AK83" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL83" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AM83" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="AN83" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11348,16 +11351,16 @@
         <v>77</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -11383,13 +11386,13 @@
         <v>77</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>77</v>
@@ -11407,7 +11410,7 @@
         <v>77</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -11422,24 +11425,24 @@
         <v>99</v>
       </c>
       <c r="AK84" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="AL84" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="AM84" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN84" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -11462,13 +11465,13 @@
         <v>77</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" s="2"/>
@@ -11519,7 +11522,7 @@
         <v>77</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -11537,7 +11540,7 @@
         <v>77</v>
       </c>
       <c r="AL85" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM85" t="s" s="2">
         <v>77</v>
@@ -11548,14 +11551,14 @@
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E86" s="2"/>
       <c r="F86" t="s" s="2">
@@ -11577,13 +11580,13 @@
         <v>132</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N86" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O86" s="2"/>
       <c r="P86" t="s" s="2">
@@ -11624,16 +11627,16 @@
         <v>135</v>
       </c>
       <c r="AC86" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD86" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE86" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -11651,7 +11654,7 @@
         <v>77</v>
       </c>
       <c r="AL86" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM86" t="s" s="2">
         <v>77</v>
@@ -11662,10 +11665,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -11688,19 +11691,19 @@
         <v>88</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N87" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="O87" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P87" t="s" s="2">
         <v>77</v>
@@ -11737,7 +11740,7 @@
         <v>77</v>
       </c>
       <c r="AB87" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AC87" s="2"/>
       <c r="AD87" t="s" s="2">
@@ -11747,7 +11750,7 @@
         <v>136</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>78</v>
@@ -11765,21 +11768,21 @@
         <v>77</v>
       </c>
       <c r="AL87" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM87" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN87" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -11802,13 +11805,13 @@
         <v>77</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N88" s="2"/>
       <c r="O88" s="2"/>
@@ -11859,7 +11862,7 @@
         <v>77</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>78</v>
@@ -11877,7 +11880,7 @@
         <v>77</v>
       </c>
       <c r="AL88" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM88" t="s" s="2">
         <v>77</v>
@@ -11888,14 +11891,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -11917,13 +11920,13 @@
         <v>132</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N89" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O89" s="2"/>
       <c r="P89" t="s" s="2">
@@ -11964,16 +11967,16 @@
         <v>135</v>
       </c>
       <c r="AC89" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD89" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE89" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>78</v>
@@ -11991,7 +11994,7 @@
         <v>77</v>
       </c>
       <c r="AL89" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM89" t="s" s="2">
         <v>77</v>
@@ -12002,10 +12005,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12031,16 +12034,16 @@
         <v>101</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>77</v>
@@ -12089,7 +12092,7 @@
         <v>77</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>78</v>
@@ -12107,21 +12110,21 @@
         <v>77</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN90" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12144,16 +12147,16 @@
         <v>88</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O91" s="2"/>
       <c r="P91" t="s" s="2">
@@ -12203,7 +12206,7 @@
         <v>77</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12221,21 +12224,21 @@
         <v>77</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN91" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12261,14 +12264,14 @@
         <v>107</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N92" s="2"/>
       <c r="O92" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>77</v>
@@ -12317,7 +12320,7 @@
         <v>77</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12335,21 +12338,21 @@
         <v>77</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN92" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12372,17 +12375,17 @@
         <v>88</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>77</v>
@@ -12431,7 +12434,7 @@
         <v>77</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -12449,21 +12452,21 @@
         <v>77</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN93" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -12486,19 +12489,19 @@
         <v>88</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O94" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>77</v>
@@ -12547,7 +12550,7 @@
         <v>77</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
@@ -12565,24 +12568,24 @@
         <v>77</v>
       </c>
       <c r="AL94" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM94" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN94" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C95" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D95" t="s" s="2">
         <v>77</v>
@@ -12604,19 +12607,19 @@
         <v>88</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N95" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O95" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>77</v>
@@ -12665,7 +12668,7 @@
         <v>77</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>78</v>
@@ -12683,21 +12686,21 @@
         <v>77</v>
       </c>
       <c r="AL95" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM95" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN95" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -12720,13 +12723,13 @@
         <v>77</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -12777,7 +12780,7 @@
         <v>77</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>78</v>
@@ -12795,7 +12798,7 @@
         <v>77</v>
       </c>
       <c r="AL96" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM96" t="s" s="2">
         <v>77</v>
@@ -12806,14 +12809,14 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E97" s="2"/>
       <c r="F97" t="s" s="2">
@@ -12835,13 +12838,13 @@
         <v>132</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N97" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O97" s="2"/>
       <c r="P97" t="s" s="2">
@@ -12882,16 +12885,16 @@
         <v>135</v>
       </c>
       <c r="AC97" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD97" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE97" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>78</v>
@@ -12909,7 +12912,7 @@
         <v>77</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>77</v>
@@ -12920,10 +12923,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -12949,16 +12952,16 @@
         <v>101</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O98" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P98" t="s" s="2">
         <v>77</v>
@@ -12968,7 +12971,7 @@
         <v>77</v>
       </c>
       <c r="S98" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="T98" t="s" s="2">
         <v>77</v>
@@ -13007,7 +13010,7 @@
         <v>77</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>78</v>
@@ -13025,21 +13028,21 @@
         <v>77</v>
       </c>
       <c r="AL98" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM98" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN98" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -13062,16 +13065,16 @@
         <v>88</v>
       </c>
       <c r="K99" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O99" s="2"/>
       <c r="P99" t="s" s="2">
@@ -13121,7 +13124,7 @@
         <v>77</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>78</v>
@@ -13139,21 +13142,21 @@
         <v>77</v>
       </c>
       <c r="AL99" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM99" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN99" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13179,14 +13182,14 @@
         <v>107</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>77</v>
@@ -13235,7 +13238,7 @@
         <v>77</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>78</v>
@@ -13253,21 +13256,21 @@
         <v>77</v>
       </c>
       <c r="AL100" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM100" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN100" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13290,17 +13293,17 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>77</v>
@@ -13349,7 +13352,7 @@
         <v>77</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>78</v>
@@ -13367,21 +13370,21 @@
         <v>77</v>
       </c>
       <c r="AL101" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM101" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN101" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -13404,19 +13407,19 @@
         <v>88</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>77</v>
@@ -13465,7 +13468,7 @@
         <v>77</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>78</v>
@@ -13483,24 +13486,24 @@
         <v>77</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN102" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C103" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="D103" t="s" s="2">
         <v>77</v>
@@ -13522,19 +13525,19 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="N103" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O103" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>77</v>
@@ -13583,7 +13586,7 @@
         <v>77</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>78</v>
@@ -13601,21 +13604,21 @@
         <v>77</v>
       </c>
       <c r="AL103" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AM103" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN103" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -13638,13 +13641,13 @@
         <v>77</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -13695,7 +13698,7 @@
         <v>77</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>78</v>
@@ -13713,7 +13716,7 @@
         <v>77</v>
       </c>
       <c r="AL104" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM104" t="s" s="2">
         <v>77</v>
@@ -13724,14 +13727,14 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E105" s="2"/>
       <c r="F105" t="s" s="2">
@@ -13753,13 +13756,13 @@
         <v>132</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -13800,16 +13803,16 @@
         <v>135</v>
       </c>
       <c r="AC105" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AD105" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE105" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>78</v>
@@ -13827,7 +13830,7 @@
         <v>77</v>
       </c>
       <c r="AL105" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM105" t="s" s="2">
         <v>77</v>
@@ -13838,10 +13841,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -13867,16 +13870,16 @@
         <v>101</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>77</v>
@@ -13886,7 +13889,7 @@
         <v>77</v>
       </c>
       <c r="S106" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="T106" t="s" s="2">
         <v>77</v>
@@ -13925,7 +13928,7 @@
         <v>77</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>78</v>
@@ -13943,21 +13946,21 @@
         <v>77</v>
       </c>
       <c r="AL106" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM106" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN106" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -13980,16 +13983,16 @@
         <v>88</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="N107" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="O107" s="2"/>
       <c r="P107" t="s" s="2">
@@ -14039,7 +14042,7 @@
         <v>77</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>78</v>
@@ -14057,21 +14060,21 @@
         <v>77</v>
       </c>
       <c r="AL107" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="AM107" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN107" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
     </row>
     <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14097,14 +14100,14 @@
         <v>107</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>77</v>
@@ -14153,7 +14156,7 @@
         <v>77</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>78</v>
@@ -14171,21 +14174,21 @@
         <v>77</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN108" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -14208,17 +14211,17 @@
         <v>88</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="N109" s="2"/>
       <c r="O109" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>77</v>
@@ -14267,7 +14270,7 @@
         <v>77</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>78</v>
@@ -14285,21 +14288,21 @@
         <v>77</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN109" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -14322,19 +14325,19 @@
         <v>88</v>
       </c>
       <c r="K110" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>77</v>
@@ -14383,7 +14386,7 @@
         <v>77</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>78</v>
@@ -14401,21 +14404,21 @@
         <v>77</v>
       </c>
       <c r="AL110" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AM110" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN110" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -14438,19 +14441,19 @@
         <v>88</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>77</v>
@@ -14499,7 +14502,7 @@
         <v>77</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>78</v>
@@ -14517,21 +14520,21 @@
         <v>77</v>
       </c>
       <c r="AL111" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="AM111" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN111" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -14554,13 +14557,13 @@
         <v>88</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" s="2"/>
@@ -14611,7 +14614,7 @@
         <v>77</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>78</v>
@@ -14629,7 +14632,7 @@
         <v>77</v>
       </c>
       <c r="AL112" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM112" t="s" s="2">
         <v>77</v>
@@ -14640,10 +14643,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -14666,16 +14669,16 @@
         <v>77</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -14725,7 +14728,7 @@
         <v>77</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>78</v>
@@ -14743,7 +14746,7 @@
         <v>77</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>77</v>
@@ -14754,10 +14757,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -14780,13 +14783,13 @@
         <v>77</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -14837,7 +14840,7 @@
         <v>77</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>78</v>
@@ -14855,7 +14858,7 @@
         <v>77</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>77</v>
@@ -14866,14 +14869,14 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E115" s="2"/>
       <c r="F115" t="s" s="2">
@@ -14895,13 +14898,13 @@
         <v>132</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N115" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O115" s="2"/>
       <c r="P115" t="s" s="2">
@@ -14951,7 +14954,7 @@
         <v>77</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>78</v>
@@ -14969,7 +14972,7 @@
         <v>77</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>77</v>
@@ -14980,14 +14983,14 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E116" s="2"/>
       <c r="F116" t="s" s="2">
@@ -15009,16 +15012,16 @@
         <v>132</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O116" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P116" t="s" s="2">
         <v>77</v>
@@ -15067,7 +15070,7 @@
         <v>77</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>78</v>
@@ -15096,10 +15099,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -15122,17 +15125,17 @@
         <v>77</v>
       </c>
       <c r="K117" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N117" s="2"/>
       <c r="O117" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P117" t="s" s="2">
         <v>77</v>
@@ -15169,7 +15172,7 @@
         <v>77</v>
       </c>
       <c r="AB117" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AC117" s="2"/>
       <c r="AD117" t="s" s="2">
@@ -15179,7 +15182,7 @@
         <v>136</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>87</v>
@@ -15194,27 +15197,27 @@
         <v>99</v>
       </c>
       <c r="AK117" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN117" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C118" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D118" t="s" s="2">
         <v>77</v>
@@ -15236,17 +15239,17 @@
         <v>77</v>
       </c>
       <c r="K118" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N118" s="2"/>
       <c r="O118" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>77</v>
@@ -15295,7 +15298,7 @@
         <v>77</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>87</v>
@@ -15310,27 +15313,27 @@
         <v>99</v>
       </c>
       <c r="AK118" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN118" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="C119" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D119" t="s" s="2">
         <v>77</v>
@@ -15352,17 +15355,17 @@
         <v>77</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>77</v>
@@ -15391,7 +15394,7 @@
       </c>
       <c r="Y119" s="2"/>
       <c r="Z119" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AA119" t="s" s="2">
         <v>77</v>
@@ -15409,7 +15412,7 @@
         <v>77</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>87</v>
@@ -15424,24 +15427,24 @@
         <v>99</v>
       </c>
       <c r="AK119" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN119" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -15464,17 +15467,17 @@
         <v>77</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>77</v>
@@ -15523,7 +15526,7 @@
         <v>77</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>78</v>
@@ -15541,7 +15544,7 @@
         <v>77</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>77</v>
@@ -15552,10 +15555,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -15578,13 +15581,13 @@
         <v>77</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15635,7 +15638,7 @@
         <v>77</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>78</v>
@@ -15650,24 +15653,24 @@
         <v>99</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN121" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15690,13 +15693,13 @@
         <v>77</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -15747,7 +15750,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -15762,10 +15765,10 @@
         <v>99</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -15776,10 +15779,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -15802,13 +15805,13 @@
         <v>77</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" s="2"/>
@@ -15859,7 +15862,7 @@
         <v>77</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
@@ -15877,7 +15880,7 @@
         <v>77</v>
       </c>
       <c r="AL123" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM123" t="s" s="2">
         <v>77</v>
@@ -15888,14 +15891,14 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
@@ -15917,13 +15920,13 @@
         <v>132</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="N124" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
@@ -15973,7 +15976,7 @@
         <v>77</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>78</v>
@@ -15991,7 +15994,7 @@
         <v>77</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>77</v>
@@ -16002,14 +16005,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -16031,16 +16034,16 @@
         <v>132</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N125" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O125" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>77</v>
@@ -16089,7 +16092,7 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
@@ -16118,10 +16121,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16144,13 +16147,13 @@
         <v>77</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16201,7 +16204,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16216,24 +16219,24 @@
         <v>99</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16256,13 +16259,13 @@
         <v>77</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -16313,7 +16316,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -16328,16 +16331,16 @@
         <v>99</v>
       </c>
       <c r="AK127" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
     </row>
   </sheetData>

--- a/currentbuild/StructureDefinition-lmdi-medication.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medication.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.0</t>
+    <t>1.1.1</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-lmdi-medication.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medication.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.2</t>
+    <t>1.1.3</t>
   </si>
   <si>
     <t>Name</t>

--- a/currentbuild/StructureDefinition-lmdi-medication.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medication.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$132</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4637" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4814" uniqueCount="478">
   <si>
     <t>Property</t>
   </si>
@@ -1383,16 +1383,69 @@
     <t>Medication.ingredient.strength</t>
   </si>
   <si>
-    <t>Quantity of ingredient present</t>
-  </si>
-  <si>
-    <t>Specifies how many (or how much) of the items there are in this Medication.  For example, 250 mg per tablet.  This is expressed as a ratio where the numerator is 250mg and the denominator is 1 tablet.</t>
+    <t>Styrken av ingrediensen i det rekvirerte/administrerte legemidlet.</t>
   </si>
   <si>
     <t>//element(*,DrugCodedType)/Strength</t>
   </si>
   <si>
     <t>RXC-3-Component Amount &amp; RXC-4-Component Units  if medication: RXO-2-Requested Give Amount - Minimum &amp; RXO-4-Requested Give Units / RXO-3-Requested Give Amount - Maximum &amp; RXO-4-Requested Give Units / RXO-11-Requested Dispense Amount &amp; RXO-12-Requested Dispense Units / RXE-3-Give Amount - Minimum &amp; RXE-5-Give Units / RXE-4-Give Amount - Maximum &amp; RXE-5-Give Units / RXE-10-Dispense Amount &amp; RXE-10-Dispense Units</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength.id</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength.extension</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength.extension:mengde</t>
+  </si>
+  <si>
+    <t>mengde</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.no/fhir/ig/lmdi/StructureDefinition/lmdi-ingredient-strength}
+</t>
+  </si>
+  <si>
+    <t>Mengde ingrediens i det rekvirerte/administrerte legemidlet.</t>
+  </si>
+  <si>
+    <t>Mengde ingrediens i det rekvirerte/administrerte legemidlet, angitt som volum eller mengde virkestoff (Quantity), eller som kode (qs, trace). Brukes i stedet for teller og nevner i strength.</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength.numerator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Quantity
+</t>
+  </si>
+  <si>
+    <t>Numerator value</t>
+  </si>
+  <si>
+    <t>The value of the numerator.</t>
+  </si>
+  <si>
+    <t>Ratio.numerator</t>
+  </si>
+  <si>
+    <t>.numerator</t>
+  </si>
+  <si>
+    <t>Medication.ingredient.strength.denominator</t>
+  </si>
+  <si>
+    <t>Denominator value</t>
+  </si>
+  <si>
+    <t>The value of the denominator.</t>
+  </si>
+  <si>
+    <t>Ratio.denominator</t>
+  </si>
+  <si>
+    <t>.denominator</t>
   </si>
   <si>
     <t>Medication.batch</t>
@@ -1769,11 +1822,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN127"/>
+  <dimension ref="A1:AN132"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="51.640625" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="32.79296875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="35.77734375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.73046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -15587,7 +15640,7 @@
         <v>440</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" s="2"/>
@@ -15653,7 +15706,7 @@
         <v>99</v>
       </c>
       <c r="AK121" t="s" s="2">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AL121" t="s" s="2">
         <v>408</v>
@@ -15662,15 +15715,15 @@
         <v>77</v>
       </c>
       <c r="AN121" t="s" s="2">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="122" hidden="true">
+      <c r="A122" t="s" s="2">
         <v>443</v>
       </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="s" s="2">
-        <v>444</v>
-      </c>
       <c r="B122" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -15684,7 +15737,7 @@
         <v>87</v>
       </c>
       <c r="H122" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I122" t="s" s="2">
         <v>77</v>
@@ -15693,13 +15746,13 @@
         <v>77</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>410</v>
+        <v>172</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>445</v>
+        <v>173</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>446</v>
+        <v>174</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" s="2"/>
@@ -15750,7 +15803,7 @@
         <v>77</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>444</v>
+        <v>175</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>78</v>
@@ -15762,13 +15815,13 @@
         <v>77</v>
       </c>
       <c r="AJ122" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK122" t="s" s="2">
-        <v>355</v>
+        <v>77</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>447</v>
+        <v>176</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>77</v>
@@ -15779,21 +15832,21 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
-        <v>77</v>
+        <v>147</v>
       </c>
       <c r="E123" s="2"/>
       <c r="F123" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G123" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H123" t="s" s="2">
         <v>77</v>
@@ -15805,15 +15858,17 @@
         <v>77</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>172</v>
+        <v>132</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>174</v>
-      </c>
-      <c r="N123" s="2"/>
+        <v>179</v>
+      </c>
+      <c r="N123" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="O123" s="2"/>
       <c r="P123" t="s" s="2">
         <v>77</v>
@@ -15850,31 +15905,31 @@
         <v>77</v>
       </c>
       <c r="AB123" t="s" s="2">
-        <v>77</v>
+        <v>135</v>
       </c>
       <c r="AC123" t="s" s="2">
-        <v>77</v>
+        <v>180</v>
       </c>
       <c r="AD123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE123" t="s" s="2">
-        <v>77</v>
+        <v>181</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH123" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI123" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ123" t="s" s="2">
-        <v>77</v>
+        <v>138</v>
       </c>
       <c r="AK123" t="s" s="2">
         <v>77</v>
@@ -15891,21 +15946,23 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>449</v>
-      </c>
-      <c r="C124" s="2"/>
+        <v>444</v>
+      </c>
+      <c r="C124" t="s" s="2">
+        <v>446</v>
+      </c>
       <c r="D124" t="s" s="2">
-        <v>147</v>
+        <v>77</v>
       </c>
       <c r="E124" s="2"/>
       <c r="F124" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G124" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H124" t="s" s="2">
         <v>77</v>
@@ -15917,17 +15974,15 @@
         <v>77</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>132</v>
+        <v>447</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>178</v>
+        <v>448</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>179</v>
-      </c>
-      <c r="N124" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>449</v>
+      </c>
+      <c r="N124" s="2"/>
       <c r="O124" s="2"/>
       <c r="P124" t="s" s="2">
         <v>77</v>
@@ -15994,7 +16049,7 @@
         <v>77</v>
       </c>
       <c r="AL124" t="s" s="2">
-        <v>176</v>
+        <v>77</v>
       </c>
       <c r="AM124" t="s" s="2">
         <v>77</v>
@@ -16012,39 +16067,35 @@
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>417</v>
+        <v>77</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G125" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I125" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J125" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>132</v>
+        <v>451</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>418</v>
+        <v>452</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>419</v>
-      </c>
-      <c r="N125" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="O125" t="s" s="2">
-        <v>151</v>
-      </c>
+        <v>453</v>
+      </c>
+      <c r="N125" s="2"/>
+      <c r="O125" s="2"/>
       <c r="P125" t="s" s="2">
         <v>77</v>
       </c>
@@ -16092,25 +16143,25 @@
         <v>77</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>420</v>
+        <v>454</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH125" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ125" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK125" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL125" t="s" s="2">
-        <v>130</v>
+        <v>455</v>
       </c>
       <c r="AM125" t="s" s="2">
         <v>77</v>
@@ -16121,10 +16172,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16144,16 +16195,16 @@
         <v>77</v>
       </c>
       <c r="J126" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>172</v>
+        <v>451</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="N126" s="2"/>
       <c r="O126" s="2"/>
@@ -16204,7 +16255,7 @@
         <v>77</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>451</v>
+        <v>459</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>78</v>
@@ -16219,24 +16270,24 @@
         <v>99</v>
       </c>
       <c r="AK126" t="s" s="2">
-        <v>355</v>
+        <v>77</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>158</v>
+        <v>460</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN126" t="s" s="2">
-        <v>454</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="127" hidden="true">
+    <row r="127">
       <c r="A127" t="s" s="2">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -16250,7 +16301,7 @@
         <v>87</v>
       </c>
       <c r="H127" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I127" t="s" s="2">
         <v>77</v>
@@ -16259,13 +16310,13 @@
         <v>77</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>456</v>
+        <v>410</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="N127" s="2"/>
       <c r="O127" s="2"/>
@@ -16316,7 +16367,7 @@
         <v>77</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>455</v>
+        <v>461</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>78</v>
@@ -16334,17 +16385,583 @@
         <v>355</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AN127" t="s" s="2">
-        <v>460</v>
+        <v>77</v>
+      </c>
+    </row>
+    <row r="128" hidden="true">
+      <c r="A128" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="B128" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C128" s="2"/>
+      <c r="D128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E128" s="2"/>
+      <c r="F128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G128" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K128" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L128" t="s" s="2">
+        <v>173</v>
+      </c>
+      <c r="M128" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="N128" s="2"/>
+      <c r="O128" s="2"/>
+      <c r="P128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q128" s="2"/>
+      <c r="R128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF128" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="AG128" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH128" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL128" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AM128" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN128" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="129" hidden="true">
+      <c r="A129" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="B129" t="s" s="2">
+        <v>466</v>
+      </c>
+      <c r="C129" s="2"/>
+      <c r="D129" t="s" s="2">
+        <v>147</v>
+      </c>
+      <c r="E129" s="2"/>
+      <c r="F129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G129" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K129" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L129" t="s" s="2">
+        <v>178</v>
+      </c>
+      <c r="M129" t="s" s="2">
+        <v>179</v>
+      </c>
+      <c r="N129" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O129" s="2"/>
+      <c r="P129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q129" s="2"/>
+      <c r="R129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF129" t="s" s="2">
+        <v>182</v>
+      </c>
+      <c r="AG129" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH129" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ129" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL129" t="s" s="2">
+        <v>176</v>
+      </c>
+      <c r="AM129" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN129" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="130" hidden="true">
+      <c r="A130" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="B130" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="C130" s="2"/>
+      <c r="D130" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="E130" s="2"/>
+      <c r="F130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I130" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="J130" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="K130" t="s" s="2">
+        <v>132</v>
+      </c>
+      <c r="L130" t="s" s="2">
+        <v>418</v>
+      </c>
+      <c r="M130" t="s" s="2">
+        <v>419</v>
+      </c>
+      <c r="N130" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="O130" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="P130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q130" s="2"/>
+      <c r="R130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF130" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="AG130" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH130" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ130" t="s" s="2">
+        <v>138</v>
+      </c>
+      <c r="AK130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AL130" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="AM130" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN130" t="s" s="2">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="131" hidden="true">
+      <c r="A131" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="B131" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="C131" s="2"/>
+      <c r="D131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E131" s="2"/>
+      <c r="F131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G131" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K131" t="s" s="2">
+        <v>172</v>
+      </c>
+      <c r="L131" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="M131" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="N131" s="2"/>
+      <c r="O131" s="2"/>
+      <c r="P131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q131" s="2"/>
+      <c r="R131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF131" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="AG131" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH131" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ131" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK131" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL131" t="s" s="2">
+        <v>158</v>
+      </c>
+      <c r="AM131" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN131" t="s" s="2">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="132" hidden="true">
+      <c r="A132" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="B132" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C132" s="2"/>
+      <c r="D132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E132" s="2"/>
+      <c r="F132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G132" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="H132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K132" t="s" s="2">
+        <v>473</v>
+      </c>
+      <c r="L132" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="M132" t="s" s="2">
+        <v>475</v>
+      </c>
+      <c r="N132" s="2"/>
+      <c r="O132" s="2"/>
+      <c r="P132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q132" s="2"/>
+      <c r="R132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF132" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="AG132" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH132" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="AI132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ132" t="s" s="2">
+        <v>99</v>
+      </c>
+      <c r="AK132" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AL132" t="s" s="2">
+        <v>476</v>
+      </c>
+      <c r="AM132" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AN132" t="s" s="2">
+        <v>477</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN127">
+  <autoFilter ref="A1:AN132">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -16354,7 +16971,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI126">
+  <conditionalFormatting sqref="A2:AI131">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/currentbuild/StructureDefinition-lmdi-medication.xlsx
+++ b/currentbuild/StructureDefinition-lmdi-medication.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>1.1.3</t>
+    <t>1.1.4</t>
   </si>
   <si>
     <t>Name</t>
